--- a/survey_templates/028_fundraiser_effectiveness_survey_form--survey_templates.xlsx
+++ b/survey_templates/028_fundraiser_effectiveness_survey_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,23 +515,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_start</t>
+          <t>fundraiser_satisfaction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>start_question</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>How satisfied are you with the fundraiser?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select one of the following options.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,41 +547,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How likely are you to recommend this event to a friend?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select one of the following options.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>enjoyment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How much did you enjoy the event?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select one of the following options.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,225 +601,76 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>expectations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How likely</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What were your expectations before attending this fundraiser?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please enter a short description.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>future_attendance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>How likely are you to attend a similar event in the future?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select one of the following options.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How would you rate the overall quality of this event?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please select one of the following options.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>question_7</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>question_8</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>question_9</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>question_10</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>question_10</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>question_11</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>question_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>question_12</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>question_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>question_13</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>question_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>question_14</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -822,12 +685,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,544 +713,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>fundraiser_satisfaction_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>fundraiser_satisfaction_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>fundraiser_satisfaction_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>fundraiser_satisfaction_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_satisfied_at_all'}</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not satisfied at all'}</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat'}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very'}</t>
+          <t>Not likely</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all'}</t>
+          <t>Not at all likely</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>enjoyment_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very'}</t>
+          <t>very_enjoyable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very'}</t>
+          <t>Very enjoyable</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>enjoyment_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat'}</t>
+          <t>somewhat_enjoyable</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat'}</t>
+          <t>Somewhat enjoyable</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>enjoyment_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very'}</t>
+          <t>not_enjoyable</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very'}</t>
+          <t>Not enjoyable</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>enjoyment_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all'}</t>
+          <t>not_at_all_enjoyable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all'}</t>
+          <t>Not at all enjoyable</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>future_attendance_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>future_attendance_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat'}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>future_attendance_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very'}</t>
+          <t>Not likely</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>future_attendance_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all'}</t>
+          <t>Not at all likely</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>quality_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>quality_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat'}</t>
+          <t>somewhat_good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat'}</t>
+          <t>Somewhat good</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>quality_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very'}</t>
+          <t>not_good</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very'}</t>
+          <t>Not good</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>quality_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all'}</t>
+          <t>not_at_all_good</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>question_11_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'very'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Very'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>question_11_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'somewhat'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Somewhat'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>question_11_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'not_very'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Not very'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>question_11_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'not_at_all'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Not at all'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'very'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Very'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'somewhat'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Somewhat'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'not_very'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Not very'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'not_at_all'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Not at all'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>question_13_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'very'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Very'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>question_13_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'somewhat'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Somewhat'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>question_13_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'not_very'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Not very'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>question_13_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'not_at_all'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Not at all'}</t>
+          <t>Not at all good</t>
         </is>
       </c>
     </row>
